--- a/output_plant/stomata_Intermediate_tesfamichael_2017.xlsx
+++ b/output_plant/stomata_Intermediate_tesfamichael_2017.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <si>
     <t>eDab</t>
   </si>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1130/G39048.1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-franks_tesfamichael_2017.xlsx</t>
+    <t xml:space="preserve">stomata-franks_tesfamichael_2017_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -643,6 +643,24 @@
   </si>
   <si>
     <t xml:space="preserve">source of measurements are not described</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilga mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-Pb age from zircons in ash interbedded with fossil plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabaceae / Cynometra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cynometra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 leaves</t>
   </si>
 </sst>
 </file>
@@ -2126,63 +2144,186 @@
       <c r="BK5" s="1"/>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="23"/>
+      <c r="A6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>27.23</v>
+      </c>
       <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="1"/>
-      <c r="AO6" s="1"/>
+      <c r="J6" s="23" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="K6" s="23" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="P6" s="26" t="n">
+        <v>515235738.714286</v>
+      </c>
+      <c r="Q6" s="26" t="n">
+        <v>24424037.9879489</v>
+      </c>
+      <c r="R6" t="s">
+        <v>215</v>
+      </c>
+      <c r="S6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>215</v>
+      </c>
+      <c r="V6" s="26" t="n">
+        <v>0.0000141642857142857</v>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0.000000383965306190452</v>
+      </c>
+      <c r="X6" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB6" s="24" t="n">
+        <v>0.00000729071428571428</v>
+      </c>
+      <c r="AC6" s="24" t="n">
+        <v>0.000000241723355375007</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AH6" s="25" t="n">
+        <v>-26.1657142857143</v>
+      </c>
+      <c r="AI6" s="25" t="n">
+        <v>0.199187123590059</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>215</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>0.000940096</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="AP6" s="23"/>
       <c r="AQ6" s="23"/>
-      <c r="AR6" s="1"/>
-      <c r="AS6" s="1"/>
-      <c r="AT6" s="1"/>
-      <c r="AU6" s="1"/>
-      <c r="AV6" s="1"/>
-      <c r="AW6" s="1"/>
-      <c r="AX6" s="1"/>
-      <c r="AY6" s="1"/>
-      <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-      <c r="BB6" s="1"/>
-      <c r="BC6" s="1"/>
-      <c r="BD6" s="1"/>
-      <c r="BE6" s="1"/>
-      <c r="BF6" s="1"/>
-      <c r="BG6" s="1"/>
-      <c r="BH6" s="1"/>
-      <c r="BI6" s="1"/>
-      <c r="BJ6" s="1"/>
+      <c r="AR6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>0.787142857142857</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>0.0144658966678538</v>
+      </c>
+      <c r="BA6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="BE6" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF6" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BG6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="BH6" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BI6" s="1" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BJ6" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="BK6" s="1"/>
     </row>
     <row r="7">
